--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:39:19+00:00</t>
+    <t>2024-03-20T14:46:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:46:52+00:00</t>
+    <t>2024-03-20T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T15:41:15+00:00</t>
+    <t>2024-03-20T17:15:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
+++ b/ig/nr-rm-useless-data/StructureDefinition-fr-core-observation-saturation-oxygen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T17:15:33+00:00</t>
+    <t>2024-03-25T10:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
